--- a/Round_Count.xlsx
+++ b/Round_Count.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,10 +450,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +516,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +527,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +582,10 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +593,10 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +604,10 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +615,10 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +626,10 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +637,10 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +648,10 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +659,10 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +670,10 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +681,10 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -703,164 +703,76 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
         <v>4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>37</v>
-      </c>
-      <c r="B32" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>38</v>
-      </c>
-      <c r="B33" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>4</v>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>7</v>
-      </c>
-      <c r="B37" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>8</v>
-      </c>
-      <c r="B38" t="n">
-        <v>6</v>
-      </c>
-      <c r="C38" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>9</v>
-      </c>
-      <c r="B39" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
